--- a/Assets/Configs/DataTables/Datas/CharacterInfo.xlsx
+++ b/Assets/Configs/DataTables/Datas/CharacterInfo.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">##var </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -64,6 +64,18 @@
   </si>
   <si>
     <t>(array#sep=,),int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModelID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模型id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -392,10 +404,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -405,8 +417,11 @@
       <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -416,8 +431,11 @@
       <c r="C2" t="s">
         <v>11</v>
       </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -425,7 +443,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -435,13 +453,19 @@
       <c r="C4" t="s">
         <v>9</v>
       </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
